--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/2022-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/2022-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BC6A6F62-B1A2-4499-80E7-5EEA7721263D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{004DF736-0663-4EEF-A70D-E65C32727DE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{B4BB7F28-2C51-439A-99F7-608B36A97198}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{F52394FA-4378-4E17-A70E-248229AB768E}"/>
   </bookViews>
   <sheets>
     <sheet name="2022-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1397,20 +1397,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA7BC0E5-D0C3-48ED-BB18-3B5F0D7D5983}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92204636-D764-47EA-81AD-8387F121035F}">
   <dimension ref="A1:R38"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="11.77734375" customWidth="1"/>
-    <col min="3" max="9" width="7.33203125" customWidth="1"/>
-    <col min="10" max="10" width="7.6640625" customWidth="1"/>
-    <col min="11" max="13" width="7.33203125" customWidth="1"/>
-    <col min="14" max="14" width="7.6640625" customWidth="1"/>
-    <col min="15" max="17" width="7.33203125" customWidth="1"/>
-    <col min="18" max="18" width="8.44140625" customWidth="1"/>
+    <col min="1" max="2" width="16.375" customWidth="1"/>
+    <col min="3" max="9" width="9" customWidth="1"/>
+    <col min="10" max="10" width="9.5" customWidth="1"/>
+    <col min="11" max="13" width="9" customWidth="1"/>
+    <col min="14" max="14" width="9.5" customWidth="1"/>
+    <col min="15" max="17" width="9" customWidth="1"/>
+    <col min="18" max="18" width="10.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
@@ -1438,7 +1438,7 @@
       <c r="Q1" s="26"/>
       <c r="R1" s="18"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="19" t="s">
         <v>1</v>
       </c>
@@ -1468,7 +1468,7 @@
       <c r="Q2" s="28"/>
       <c r="R2" s="29"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
         <v>2</v>
       </c>
@@ -1514,7 +1514,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="21"/>
       <c r="B4" s="22"/>
       <c r="C4" s="7"/>
@@ -1564,7 +1564,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="33">
         <v>2025</v>
       </c>
@@ -1618,7 +1618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="35">
         <v>2024</v>
       </c>
@@ -1672,7 +1672,7 @@
         <v>1.76</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="33">
         <v>2023</v>
       </c>
@@ -1726,7 +1726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="35">
         <v>2022</v>
       </c>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="33">
         <v>2021</v>
       </c>
@@ -1834,7 +1834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="35">
         <v>2020</v>
       </c>
@@ -1888,7 +1888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="33">
         <v>2019</v>
       </c>
@@ -1942,7 +1942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="35">
         <v>2018</v>
       </c>
@@ -1996,7 +1996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="33">
         <v>2017</v>
       </c>
@@ -2050,7 +2050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="35">
         <v>2016</v>
       </c>
@@ -2104,7 +2104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="33">
         <v>2015</v>
       </c>
@@ -2158,7 +2158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="35">
         <v>2014</v>
       </c>
@@ -2212,7 +2212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="33">
         <v>2013</v>
       </c>
@@ -2266,7 +2266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="35">
         <v>2012</v>
       </c>
@@ -2320,7 +2320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="33">
         <v>2011</v>
       </c>
@@ -2374,7 +2374,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="35">
         <v>2010</v>
       </c>
@@ -2428,7 +2428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="33">
         <v>2009</v>
       </c>
@@ -2482,7 +2482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="35">
         <v>2008</v>
       </c>
@@ -2536,7 +2536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="33">
         <v>2007</v>
       </c>
@@ -2590,7 +2590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="35">
         <v>2006</v>
       </c>
@@ -2644,7 +2644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="33">
         <v>2005</v>
       </c>
@@ -2698,7 +2698,7 @@
         <v>6.49</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="35">
         <v>2004</v>
       </c>
@@ -2752,7 +2752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="33">
         <v>2003</v>
       </c>
@@ -2806,7 +2806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="35">
         <v>2002</v>
       </c>
@@ -2860,7 +2860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="33">
         <v>2001</v>
       </c>
@@ -2914,7 +2914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="35">
         <v>2000</v>
       </c>
@@ -2968,7 +2968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="33">
         <v>1999</v>
       </c>
@@ -3022,7 +3022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="35">
         <v>1998</v>
       </c>
@@ -3076,7 +3076,7 @@
         <v>2.93</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="33">
         <v>1997</v>
       </c>
@@ -3130,7 +3130,7 @@
         <v>4.33</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="35">
         <v>1996</v>
       </c>
@@ -3184,7 +3184,7 @@
         <v>7.38</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="33">
         <v>1995</v>
       </c>
@@ -3238,7 +3238,7 @@
         <v>4.16</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="35">
         <v>1994</v>
       </c>
@@ -3292,7 +3292,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="33">
         <v>1993</v>
       </c>
@@ -3346,7 +3346,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="35" t="s">
         <v>25</v>
       </c>
